--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I613"/>
+  <dimension ref="A1:I617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20665,6 +20665,138 @@
         <v>379.34</v>
       </c>
       <c r="I613" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>315.53</v>
+      </c>
+      <c r="C614" t="n">
+        <v>343.07</v>
+      </c>
+      <c r="D614" t="n">
+        <v>348.17</v>
+      </c>
+      <c r="E614" t="n">
+        <v>349.76</v>
+      </c>
+      <c r="F614" t="n">
+        <v>357.78</v>
+      </c>
+      <c r="G614" t="n">
+        <v>373.22</v>
+      </c>
+      <c r="H614" t="n">
+        <v>379.14</v>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>315.53</v>
+      </c>
+      <c r="C615" t="n">
+        <v>343.07</v>
+      </c>
+      <c r="D615" t="n">
+        <v>348.17</v>
+      </c>
+      <c r="E615" t="n">
+        <v>349.76</v>
+      </c>
+      <c r="F615" t="n">
+        <v>357.78</v>
+      </c>
+      <c r="G615" t="n">
+        <v>373.22</v>
+      </c>
+      <c r="H615" t="n">
+        <v>379.02</v>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>312.88</v>
+      </c>
+      <c r="C616" t="n">
+        <v>342.33</v>
+      </c>
+      <c r="D616" t="n">
+        <v>347.53</v>
+      </c>
+      <c r="E616" t="n">
+        <v>349.42</v>
+      </c>
+      <c r="F616" t="n">
+        <v>358.39</v>
+      </c>
+      <c r="G616" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="H616" t="n">
+        <v>379</v>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="C617" t="n">
+        <v>342.82</v>
+      </c>
+      <c r="D617" t="n">
+        <v>348</v>
+      </c>
+      <c r="E617" t="n">
+        <v>349.4</v>
+      </c>
+      <c r="F617" t="n">
+        <v>358.17</v>
+      </c>
+      <c r="G617" t="n">
+        <v>373.85</v>
+      </c>
+      <c r="H617" t="n">
+        <v>379.03</v>
+      </c>
+      <c r="I617" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20681,7 +20813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B636"/>
+  <dimension ref="A1:B642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27044,6 +27176,66 @@
       </c>
       <c r="B636" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -27212,28 +27404,28 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2472426649577125</v>
+        <v>-0.2785354457023489</v>
       </c>
       <c r="J2" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K2" t="n">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0311934619491826</v>
+        <v>0.03843724724401887</v>
       </c>
       <c r="M2" t="n">
-        <v>8.379575151464298</v>
+        <v>8.491782419623743</v>
       </c>
       <c r="N2" t="n">
-        <v>100.3092317960676</v>
+        <v>103.3256500591255</v>
       </c>
       <c r="O2" t="n">
-        <v>10.01544965521107</v>
+        <v>10.16492253089641</v>
       </c>
       <c r="P2" t="n">
-        <v>344.9814743379363</v>
+        <v>345.3323908957239</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27290,28 +27482,28 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1622080289336102</v>
+        <v>-0.1678422375608081</v>
       </c>
       <c r="J3" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K3" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1750766666259372</v>
+        <v>0.1845283945866577</v>
       </c>
       <c r="M3" t="n">
-        <v>2.107590866464538</v>
+        <v>2.116939340721212</v>
       </c>
       <c r="N3" t="n">
-        <v>6.623547654527593</v>
+        <v>6.701751455719661</v>
       </c>
       <c r="O3" t="n">
-        <v>2.573625391257942</v>
+        <v>2.588774122189818</v>
       </c>
       <c r="P3" t="n">
-        <v>351.5374522134616</v>
+        <v>351.600170705659</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27368,28 +27560,28 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1309817762484876</v>
+        <v>-0.1323501531152176</v>
       </c>
       <c r="J4" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K4" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1297110008511323</v>
+        <v>0.1335532517889394</v>
       </c>
       <c r="M4" t="n">
-        <v>1.96797707104599</v>
+        <v>1.962337365051816</v>
       </c>
       <c r="N4" t="n">
-        <v>6.149914631324685</v>
+        <v>6.117534981013288</v>
       </c>
       <c r="O4" t="n">
-        <v>2.479902141481531</v>
+        <v>2.47336511275899</v>
       </c>
       <c r="P4" t="n">
-        <v>352.5448090849247</v>
+        <v>352.5600420421005</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27446,28 +27638,28 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1126812676948684</v>
+        <v>-0.1106847861797712</v>
       </c>
       <c r="J5" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K5" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1207842466316683</v>
+        <v>0.1181740034395681</v>
       </c>
       <c r="M5" t="n">
-        <v>1.722919423881625</v>
+        <v>1.723057039471989</v>
       </c>
       <c r="N5" t="n">
-        <v>4.937979324599879</v>
+        <v>4.921267430644868</v>
       </c>
       <c r="O5" t="n">
-        <v>2.222156458172979</v>
+        <v>2.218392983816183</v>
       </c>
       <c r="P5" t="n">
-        <v>351.072932312671</v>
+        <v>351.0507109317955</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27524,28 +27716,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02082234797890162</v>
+        <v>-0.01645472929179693</v>
       </c>
       <c r="J6" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K6" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005063715396594892</v>
+        <v>0.003162137592883862</v>
       </c>
       <c r="M6" t="n">
-        <v>1.677844387774476</v>
+        <v>1.689503985491837</v>
       </c>
       <c r="N6" t="n">
-        <v>4.551410779506344</v>
+        <v>4.594787188325966</v>
       </c>
       <c r="O6" t="n">
-        <v>2.13340356695735</v>
+        <v>2.143545471485493</v>
       </c>
       <c r="P6" t="n">
-        <v>355.2137163458692</v>
+        <v>355.1650958171047</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27602,28 +27794,28 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1338132210097054</v>
+        <v>-0.128771049204729</v>
       </c>
       <c r="J7" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K7" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1215717268497452</v>
+        <v>0.1136042477641703</v>
       </c>
       <c r="M7" t="n">
-        <v>2.077280375022734</v>
+        <v>2.085882686137704</v>
       </c>
       <c r="N7" t="n">
-        <v>6.912456667858034</v>
+        <v>6.964817167109537</v>
       </c>
       <c r="O7" t="n">
-        <v>2.629155124342806</v>
+        <v>2.639094004977757</v>
       </c>
       <c r="P7" t="n">
-        <v>373.2379992686229</v>
+        <v>373.1818683370764</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27680,28 +27872,28 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1292497537796593</v>
+        <v>-0.1338565608338306</v>
       </c>
       <c r="J8" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K8" t="n">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05914279313749515</v>
+        <v>0.06365962903398126</v>
       </c>
       <c r="M8" t="n">
-        <v>2.971254599925389</v>
+        <v>2.972912929781823</v>
       </c>
       <c r="N8" t="n">
-        <v>14.19848432052569</v>
+        <v>14.18695287465344</v>
       </c>
       <c r="O8" t="n">
-        <v>3.768087621131665</v>
+        <v>3.766557164660246</v>
       </c>
       <c r="P8" t="n">
-        <v>386.0829612882076</v>
+        <v>386.1342420104095</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27739,7 +27931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I613"/>
+  <dimension ref="A1:I617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56545,6 +56737,194 @@
         </is>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>-36.63905566204792,174.75070745360438</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>-36.63962057928337,174.7500711630365</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>-36.64004052976824,174.7493229243724</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>-36.64051174445447,174.74863462953013</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>-36.641046617335405,174.74802455210838</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>-36.641599948938484,174.74744797557392</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>-36.64215274335566,174.7468964406147</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>-36.63905566204792,174.75070745360438</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>-36.63962057928337,174.7500711630365</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>-36.64004052976824,174.7493229243724</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>-36.64051174445447,174.74863462953013</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-36.641046617335405,174.74802455210838</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>-36.641599948938484,174.74744797557392</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>-36.642152016664625,174.74689544672287</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>-36.63903490061821,174.75069280641452</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>-36.639614855859726,174.7500669151787</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>-36.64003587161275,174.7493187036357</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>-36.64050944429464,174.74863211742408</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>-36.64105075547212,174.74802904306074</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-36.641604113316376,174.74745292769282</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>-36.64215189554947,174.74689528107425</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>-36.63904054145971,174.7506967860276</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>-36.63961864569432,174.75006972794935</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>-36.64003929244571,174.74932180323916</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>-36.64050930899112,174.74863196965313</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>-36.64104926302939,174.74802742337292</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>-36.64160404824797,174.74745285031597</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>-36.642152077222214,174.7468955295472</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I617"/>
+  <dimension ref="A1:I621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20797,6 +20797,138 @@
         <v>379.03</v>
       </c>
       <c r="I617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="C618" t="n">
+        <v>342.7</v>
+      </c>
+      <c r="D618" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="E618" t="n">
+        <v>349.43</v>
+      </c>
+      <c r="F618" t="n">
+        <v>358.18</v>
+      </c>
+      <c r="G618" t="n">
+        <v>373.77</v>
+      </c>
+      <c r="H618" t="n">
+        <v>379.19</v>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="C619" t="n">
+        <v>343.52</v>
+      </c>
+      <c r="D619" t="n">
+        <v>348.37</v>
+      </c>
+      <c r="E619" t="n">
+        <v>349.96</v>
+      </c>
+      <c r="F619" t="n">
+        <v>358.29</v>
+      </c>
+      <c r="G619" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="H619" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>312.63</v>
+      </c>
+      <c r="C620" t="n">
+        <v>344.07</v>
+      </c>
+      <c r="D620" t="n">
+        <v>348.6</v>
+      </c>
+      <c r="E620" t="n">
+        <v>350.05</v>
+      </c>
+      <c r="F620" t="n">
+        <v>358.53</v>
+      </c>
+      <c r="G620" t="n">
+        <v>375.16</v>
+      </c>
+      <c r="H620" t="n">
+        <v>380.29</v>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>310.77</v>
+      </c>
+      <c r="C621" t="n">
+        <v>342.96</v>
+      </c>
+      <c r="D621" t="n">
+        <v>347.09</v>
+      </c>
+      <c r="E621" t="n">
+        <v>348.97</v>
+      </c>
+      <c r="F621" t="n">
+        <v>357.71</v>
+      </c>
+      <c r="G621" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="H621" t="n">
+        <v>379.12</v>
+      </c>
+      <c r="I621" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20813,7 +20945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B642"/>
+  <dimension ref="A1:B647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27236,6 +27368,56 @@
       </c>
       <c r="B642" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -27404,28 +27586,28 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2785354457023489</v>
+        <v>-0.3111305066263154</v>
       </c>
       <c r="J2" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="K2" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03843724724401887</v>
+        <v>0.04640284126080474</v>
       </c>
       <c r="M2" t="n">
-        <v>8.491782419623743</v>
+        <v>8.611867371131838</v>
       </c>
       <c r="N2" t="n">
-        <v>103.3256500591255</v>
+        <v>106.7057044794163</v>
       </c>
       <c r="O2" t="n">
-        <v>10.16492253089641</v>
+        <v>10.32984532698415</v>
       </c>
       <c r="P2" t="n">
-        <v>345.3323908957239</v>
+        <v>345.6993209015942</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27482,28 +27664,28 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1678422375608081</v>
+        <v>-0.1726516631840294</v>
       </c>
       <c r="J3" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="K3" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1845283945866577</v>
+        <v>0.1932323403602838</v>
       </c>
       <c r="M3" t="n">
-        <v>2.116939340721212</v>
+        <v>2.122953325695586</v>
       </c>
       <c r="N3" t="n">
-        <v>6.701751455719661</v>
+        <v>6.749773390705633</v>
       </c>
       <c r="O3" t="n">
-        <v>2.588774122189818</v>
+        <v>2.598032600008251</v>
       </c>
       <c r="P3" t="n">
-        <v>351.600170705659</v>
+        <v>351.6539127858892</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27560,28 +27742,28 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1323501531152176</v>
+        <v>-0.1336222564654679</v>
       </c>
       <c r="J4" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="K4" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1335532517889394</v>
+        <v>0.137262591058579</v>
       </c>
       <c r="M4" t="n">
-        <v>1.962337365051816</v>
+        <v>1.956294364010262</v>
       </c>
       <c r="N4" t="n">
-        <v>6.117534981013288</v>
+        <v>6.08643562656841</v>
       </c>
       <c r="O4" t="n">
-        <v>2.47336511275899</v>
+        <v>2.467070251648382</v>
       </c>
       <c r="P4" t="n">
-        <v>352.5600420421005</v>
+        <v>352.5742624455193</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27638,28 +27820,28 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1106847861797712</v>
+        <v>-0.1087177781497948</v>
       </c>
       <c r="J5" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="K5" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1181740034395681</v>
+        <v>0.1155692810960381</v>
       </c>
       <c r="M5" t="n">
-        <v>1.723057039471989</v>
+        <v>1.723113284353626</v>
       </c>
       <c r="N5" t="n">
-        <v>4.921267430644868</v>
+        <v>4.905706215361763</v>
       </c>
       <c r="O5" t="n">
-        <v>2.218392983816183</v>
+        <v>2.214882889762292</v>
       </c>
       <c r="P5" t="n">
-        <v>351.0507109317955</v>
+        <v>351.0287336863165</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27716,28 +27898,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01645472929179693</v>
+        <v>-0.01203718643696596</v>
       </c>
       <c r="J6" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="K6" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003162137592883862</v>
+        <v>0.001690310624125613</v>
       </c>
       <c r="M6" t="n">
-        <v>1.689503985491837</v>
+        <v>1.702288923612622</v>
       </c>
       <c r="N6" t="n">
-        <v>4.594787188325966</v>
+        <v>4.641172738104436</v>
       </c>
       <c r="O6" t="n">
-        <v>2.143545471485493</v>
+        <v>2.154338120654332</v>
       </c>
       <c r="P6" t="n">
-        <v>355.1650958171047</v>
+        <v>355.1157337574065</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27794,28 +27976,28 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.128771049204729</v>
+        <v>-0.1230432033460679</v>
       </c>
       <c r="J7" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="K7" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1136042477641703</v>
+        <v>0.104332675924616</v>
       </c>
       <c r="M7" t="n">
-        <v>2.085882686137704</v>
+        <v>2.097363282533543</v>
       </c>
       <c r="N7" t="n">
-        <v>6.964817167109537</v>
+        <v>7.048888415297906</v>
       </c>
       <c r="O7" t="n">
-        <v>2.639094004977757</v>
+        <v>2.654974277709279</v>
       </c>
       <c r="P7" t="n">
-        <v>373.1818683370764</v>
+        <v>373.1178602733841</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27872,28 +28054,28 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1338565608338306</v>
+        <v>-0.1376787464793946</v>
       </c>
       <c r="J8" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="K8" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06365962903398126</v>
+        <v>0.06771770918421638</v>
       </c>
       <c r="M8" t="n">
-        <v>2.972912929781823</v>
+        <v>2.970966038926956</v>
       </c>
       <c r="N8" t="n">
-        <v>14.18695287465344</v>
+        <v>14.15330860473214</v>
       </c>
       <c r="O8" t="n">
-        <v>3.766557164660246</v>
+        <v>3.762088330267132</v>
       </c>
       <c r="P8" t="n">
-        <v>386.1342420104095</v>
+        <v>386.1769528427508</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27931,7 +28113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I617"/>
+  <dimension ref="A1:I621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56925,6 +57107,194 @@
         </is>
       </c>
     </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>-36.6390393662844,174.75069595694148</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>-36.63961771757157,174.75006903910753</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>-36.64003871017628,174.74932127564705</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>-36.6405095119464,174.74863219130955</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>-36.641049330867695,174.74802749699512</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>-36.64160352770076,174.74745223130108</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>-36.642153046143584,174.74689685473632</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>-36.6390393662844,174.75069595694148</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>-36.63962405974361,174.75007374619358</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>-36.64004198544179,174.74932424335267</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>-36.64051309748965,174.74863610723966</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>-36.64105007708906,174.748028306839</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>-36.641605805094834,174.7474549394913</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>-36.64215522621659,174.7468998364119</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>-36.63903294199267,174.75069142460458</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>-36.63962831363937,174.7500769033859</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>-36.640043659466365,174.7493257601801</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>-36.64051370635548,174.74863677220895</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>-36.64105170520838,174.74803007377116</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>-36.64161257220826,174.74746298668597</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>-36.64215970747753,174.74690596541228</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>-36.63901836981799,174.75068114394082</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>-36.639619728504194,174.75007053159814</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>-36.64003266913077,174.74931580187953</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>-36.640506399965346,174.74862879257805</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>-36.641046142467246,174.74802403675324</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-36.641603137290325,174.7474517670399</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>-36.64215262224049,174.74689627496608</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0148/nzd0148.xlsx
+++ b/data/nzd0148/nzd0148.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I621"/>
+  <dimension ref="A1:I622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20929,6 +20929,39 @@
         <v>379.12</v>
       </c>
       <c r="I621" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>312.06</v>
+      </c>
+      <c r="C622" t="n">
+        <v>343.55</v>
+      </c>
+      <c r="D622" t="n">
+        <v>347.44</v>
+      </c>
+      <c r="E622" t="n">
+        <v>349.46</v>
+      </c>
+      <c r="F622" t="n">
+        <v>357.93</v>
+      </c>
+      <c r="G622" t="n">
+        <v>374.01</v>
+      </c>
+      <c r="H622" t="n">
+        <v>379.27</v>
+      </c>
+      <c r="I622" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20945,7 +20978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B647"/>
+  <dimension ref="A1:B648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27418,6 +27451,16 @@
       </c>
       <c r="B647" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>
@@ -27586,28 +27629,28 @@
         <v>0.0456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3111305066263154</v>
+        <v>-0.3192918406001298</v>
       </c>
       <c r="J2" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K2" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04640284126080474</v>
+        <v>0.04846896803103717</v>
       </c>
       <c r="M2" t="n">
-        <v>8.611867371131838</v>
+        <v>8.642213871886495</v>
       </c>
       <c r="N2" t="n">
-        <v>106.7057044794163</v>
+        <v>107.555546852619</v>
       </c>
       <c r="O2" t="n">
-        <v>10.32984532698415</v>
+        <v>10.37089903781823</v>
       </c>
       <c r="P2" t="n">
-        <v>345.6993209015942</v>
+        <v>345.791507299084</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27664,28 +27707,28 @@
         <v>0.0598</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1726516631840294</v>
+        <v>-0.173751113191583</v>
       </c>
       <c r="J3" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K3" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1932323403602838</v>
+        <v>0.1953267755183681</v>
       </c>
       <c r="M3" t="n">
-        <v>2.122953325695586</v>
+        <v>2.123994307933028</v>
       </c>
       <c r="N3" t="n">
-        <v>6.749773390705633</v>
+        <v>6.757756149280363</v>
       </c>
       <c r="O3" t="n">
-        <v>2.598032600008251</v>
+        <v>2.599568454432459</v>
       </c>
       <c r="P3" t="n">
-        <v>351.6539127858892</v>
+        <v>351.6662415090175</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27742,28 +27785,28 @@
         <v>0.0619</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1336222564654679</v>
+        <v>-0.134110497171449</v>
       </c>
       <c r="J4" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K4" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L4" t="n">
-        <v>0.137262591058579</v>
+        <v>0.138470293930132</v>
       </c>
       <c r="M4" t="n">
-        <v>1.956294364010262</v>
+        <v>1.955698004292285</v>
       </c>
       <c r="N4" t="n">
-        <v>6.08643562656841</v>
+        <v>6.080352295645328</v>
       </c>
       <c r="O4" t="n">
-        <v>2.467070251648382</v>
+        <v>2.465837037528094</v>
       </c>
       <c r="P4" t="n">
-        <v>352.5742624455193</v>
+        <v>352.579737350647</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27820,28 +27863,28 @@
         <v>0.0585</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1087177781497948</v>
+        <v>-0.1082766667018298</v>
       </c>
       <c r="J5" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K5" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1155692810960381</v>
+        <v>0.1150314332862852</v>
       </c>
       <c r="M5" t="n">
-        <v>1.723113284353626</v>
+        <v>1.722848631344096</v>
       </c>
       <c r="N5" t="n">
-        <v>4.905706215361763</v>
+        <v>4.9008411324111</v>
       </c>
       <c r="O5" t="n">
-        <v>2.214882889762292</v>
+        <v>2.21378434641026</v>
       </c>
       <c r="P5" t="n">
-        <v>351.0287336863165</v>
+        <v>351.0237872668583</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27898,28 +27941,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01203718643696596</v>
+        <v>-0.01103215429974996</v>
       </c>
       <c r="J6" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K6" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001690310624125613</v>
+        <v>0.001420336176793602</v>
       </c>
       <c r="M6" t="n">
-        <v>1.702288923612622</v>
+        <v>1.704969457278725</v>
       </c>
       <c r="N6" t="n">
-        <v>4.641172738104436</v>
+        <v>4.649452107465351</v>
       </c>
       <c r="O6" t="n">
-        <v>2.154338120654332</v>
+        <v>2.156258822002904</v>
       </c>
       <c r="P6" t="n">
-        <v>355.1157337574065</v>
+        <v>355.1044637925425</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27976,28 +28019,28 @@
         <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1230432033460679</v>
+        <v>-0.1216917566960387</v>
       </c>
       <c r="J7" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K7" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L7" t="n">
-        <v>0.104332675924616</v>
+        <v>0.1022349953572527</v>
       </c>
       <c r="M7" t="n">
-        <v>2.097363282533543</v>
+        <v>2.099849094928233</v>
       </c>
       <c r="N7" t="n">
-        <v>7.048888415297906</v>
+        <v>7.066021702132927</v>
       </c>
       <c r="O7" t="n">
-        <v>2.654974277709279</v>
+        <v>2.658198958342457</v>
       </c>
       <c r="P7" t="n">
-        <v>373.1178602733841</v>
+        <v>373.1027057766298</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28054,28 +28097,28 @@
         <v>0.0301</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1376787464793946</v>
+        <v>-0.138699502146416</v>
       </c>
       <c r="J8" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K8" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06771770918421638</v>
+        <v>0.0688054110696813</v>
       </c>
       <c r="M8" t="n">
-        <v>2.970966038926956</v>
+        <v>2.970793408424705</v>
       </c>
       <c r="N8" t="n">
-        <v>14.15330860473214</v>
+        <v>14.14676728834127</v>
       </c>
       <c r="O8" t="n">
-        <v>3.762088330267132</v>
+        <v>3.761218856745945</v>
       </c>
       <c r="P8" t="n">
-        <v>386.1769528427508</v>
+        <v>386.1883991239951</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28113,7 +28156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I621"/>
+  <dimension ref="A1:I622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57295,6 +57338,53 @@
         </is>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-36.63902847632635,174.7506882740782</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>-36.63962429177429,174.75007391840404</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>-36.64003521655963,174.74931811009463</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>-36.64050971490168,174.74863241296597</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>-36.64104763491003,174.7480256564409</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>-36.641605089342406,174.74745408834576</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>-36.64215353060426,174.74689751733086</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
